--- a/MuleSoft_Job_Tracker.xlsx
+++ b/MuleSoft_Job_Tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet name="MuleSoft Jobs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'MuleSoft Jobs'!$A$1:$F$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'MuleSoft Jobs'!$A$1:$F$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -691,8 +691,40 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08 12:24 IST</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise Integration | Anypoint Platform | Mulesoft</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise Integration | Anypoint Platform | Mulesoft</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>India / verify posting</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>47/100 — Matched profile skills: mulesoft, anypoint. Score 47/100.</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>https://bing.com/ck/a</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F8"/>
+  <autoFilter ref="A1:F9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MuleSoft_Job_Tracker.xlsx
+++ b/MuleSoft_Job_Tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet name="MuleSoft Jobs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'MuleSoft Jobs'!$A$1:$F$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'MuleSoft Jobs'!$A$1:$F$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -691,40 +691,8 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-08 12:24 IST</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise Integration | Anypoint Platform | Mulesoft</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise Integration | Anypoint Platform | Mulesoft</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>India / verify posting</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>47/100 — Matched profile skills: mulesoft, anypoint. Score 47/100.</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>https://bing.com/ck/a</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F9"/>
+  <autoFilter ref="A1:F8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MuleSoft_Job_Tracker.xlsx
+++ b/MuleSoft_Job_Tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet name="MuleSoft Jobs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'MuleSoft Jobs'!$A$1:$F$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'MuleSoft Jobs'!$A$1:$F$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -470,32 +470,32 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08 09:46 IST</t>
+          <t>2026-10-08 13:40 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>PwC Acceleration Center India</t>
+          <t>Enterprise Integration | Anypoint Platform | Mulesoft</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>MuleSoft Developer - Associate</t>
+          <t>Enterprise Integration | Anypoint Platform | Mulesoft</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru East, Karnataka, India</t>
+          <t>India / verify posting</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>98/100 — Excellent match: 2+ years required; Mule 4, RAML, API-led connectivity, DataWeave 2.0, Anypoint Platform, CloudHub, MUnit, SFTP/HTTP/SOAP/database connectors and API security.</t>
+          <t>47/100 — Matched profile skills: mulesoft, anypoint. Score 47/100.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/mulesoft-developer-associate-at-pwc-acceleration-center-india-4458071876</t>
+          <t>https://mulesoft.com/platform/enterprise-integration</t>
         </is>
       </c>
     </row>
@@ -517,17 +517,17 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Chennai, Tamil Nadu, India</t>
+          <t>Bengaluru East, Karnataka, India</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>98/100 — Excellent match: 2+ years required and the posting explicitly lists Mule 4, RAML, API-led connectivity, DataWeave 2.0, Anypoint Platform, MUnit and enterprise connectors.</t>
+          <t>98/100 — Excellent match: 2+ years required; Mule 4, RAML, API-led connectivity, DataWeave 2.0, Anypoint Platform, CloudHub, MUnit, SFTP/HTTP/SOAP/database connectors and API security.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/mulesoft-developer-associate-at-pwc-acceleration-center-india-4470181194</t>
+          <t>https://in.linkedin.com/jobs/view/mulesoft-developer-associate-at-pwc-acceleration-center-india-4458071876</t>
         </is>
       </c>
     </row>
@@ -539,27 +539,27 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>NTT DATA North America</t>
+          <t>PwC Acceleration Center India</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Mulesoft Developer</t>
+          <t>MuleSoft Developer - Associate</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Delhi, Delhi, India</t>
+          <t>Chennai, Tamil Nadu, India</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>96/100 — Strong match: minimum 2+ years with MuleSoft Anypoint Platform; RAML, MUnit, SOAP/REST APIs, batch processes and relational databases are explicitly required/preferred.</t>
+          <t>98/100 — Excellent match: 2+ years required and the posting explicitly lists Mule 4, RAML, API-led connectivity, DataWeave 2.0, Anypoint Platform, MUnit and enterprise connectors.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/mulesoft-developer-at-ntt-data-north-america-4466090559</t>
+          <t>https://in.linkedin.com/jobs/view/mulesoft-developer-associate-at-pwc-acceleration-center-india-4470181194</t>
         </is>
       </c>
     </row>
@@ -571,27 +571,27 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>NTT DATA North America</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Custom Software Engineer</t>
+          <t>Mulesoft Developer</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru, Karnataka, India</t>
+          <t>Delhi, Delhi, India</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>94/100 — Strong match: 2–5 year band, minimum 3 years MuleSoft Anypoint Platform, API design, integration patterns and cloud deployment.</t>
+          <t>96/100 — Strong match: minimum 2+ years with MuleSoft Anypoint Platform; RAML, MUnit, SOAP/REST APIs, batch processes and relational databases are explicitly required/preferred.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>https://www.accenture.com/in-en/careers/jobdetails?id=ATCI-5378805-S1962637_en</t>
+          <t>https://in.linkedin.com/jobs/view/mulesoft-developer-at-ntt-data-north-america-4466090559</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>https://www.accenture.com/in-en/careers/jobdetails?id=ATCI-5222068-S1915736_en</t>
+          <t>https://www.accenture.com/in-en/careers/jobdetails?id=ATCI-5378805-S1962637_en</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Chennai, Tamil Nadu, India</t>
+          <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>https://www.accenture.com/in-en/careers/jobdetails?id=ATCI-5192534-S1909174_en</t>
+          <t>https://www.accenture.com/in-en/careers/jobdetails?id=ATCI-5222068-S1915736_en</t>
         </is>
       </c>
     </row>
@@ -672,27 +672,59 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>Custom Software Engineer</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>94/100 — Strong match: 2–5 year band, minimum 3 years MuleSoft Anypoint Platform, API design, integration patterns and cloud deployment.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.accenture.com/in-en/careers/jobdetails?id=ATCI-5192534-S1909174_en</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08 09:46 IST</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
           <t>Application Developer</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>93/100 — Strong match: 2–5 year band and minimum 3 years MuleSoft Anypoint Platform, with API design, integration, API management and cloud deployment.</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>https://www.accenture.com/in-en/careers/jobdetails?id=ATCI-5106832-S1903314_en</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F8"/>
+  <autoFilter ref="A1:F9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MuleSoft_Job_Tracker.xlsx
+++ b/MuleSoft_Job_Tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet name="MuleSoft Jobs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'MuleSoft Jobs'!$A$1:$F$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'MuleSoft Jobs'!$A$1:$F$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -470,17 +470,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08 13:40 IST</t>
+          <t>2026-10-08 23:25 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Enterprise Integration | Anypoint Platform | Mulesoft</t>
+          <t>API Management Platform | Mulesoft</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Enterprise Integration | Anypoint Platform | Mulesoft</t>
+          <t>API Management Platform | Mulesoft</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -495,39 +495,39 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>https://mulesoft.com/platform/enterprise-integration</t>
+          <t>https://mulesoft.com/api/management</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08 09:46 IST</t>
+          <t>2026-10-08 13:40 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>PwC Acceleration Center India</t>
+          <t>Enterprise Integration | Anypoint Platform | Mulesoft</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>MuleSoft Developer - Associate</t>
+          <t>Enterprise Integration | Anypoint Platform | Mulesoft</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru East, Karnataka, India</t>
+          <t>India / verify posting</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>98/100 — Excellent match: 2+ years required; Mule 4, RAML, API-led connectivity, DataWeave 2.0, Anypoint Platform, CloudHub, MUnit, SFTP/HTTP/SOAP/database connectors and API security.</t>
+          <t>47/100 — Matched profile skills: mulesoft, anypoint. Score 47/100.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/mulesoft-developer-associate-at-pwc-acceleration-center-india-4458071876</t>
+          <t>https://mulesoft.com/platform/enterprise-integration</t>
         </is>
       </c>
     </row>
@@ -549,17 +549,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Chennai, Tamil Nadu, India</t>
+          <t>Bengaluru East, Karnataka, India</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>98/100 — Excellent match: 2+ years required and the posting explicitly lists Mule 4, RAML, API-led connectivity, DataWeave 2.0, Anypoint Platform, MUnit and enterprise connectors.</t>
+          <t>98/100 — Excellent match: 2+ years required; Mule 4, RAML, API-led connectivity, DataWeave 2.0, Anypoint Platform, CloudHub, MUnit, SFTP/HTTP/SOAP/database connectors and API security.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/mulesoft-developer-associate-at-pwc-acceleration-center-india-4470181194</t>
+          <t>https://in.linkedin.com/jobs/view/mulesoft-developer-associate-at-pwc-acceleration-center-india-4458071876</t>
         </is>
       </c>
     </row>
@@ -571,27 +571,27 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>NTT DATA North America</t>
+          <t>PwC Acceleration Center India</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Mulesoft Developer</t>
+          <t>MuleSoft Developer - Associate</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Delhi, Delhi, India</t>
+          <t>Chennai, Tamil Nadu, India</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>96/100 — Strong match: minimum 2+ years with MuleSoft Anypoint Platform; RAML, MUnit, SOAP/REST APIs, batch processes and relational databases are explicitly required/preferred.</t>
+          <t>98/100 — Excellent match: 2+ years required and the posting explicitly lists Mule 4, RAML, API-led connectivity, DataWeave 2.0, Anypoint Platform, MUnit and enterprise connectors.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/mulesoft-developer-at-ntt-data-north-america-4466090559</t>
+          <t>https://in.linkedin.com/jobs/view/mulesoft-developer-associate-at-pwc-acceleration-center-india-4470181194</t>
         </is>
       </c>
     </row>
@@ -603,27 +603,27 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>NTT DATA North America</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Custom Software Engineer</t>
+          <t>Mulesoft Developer</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru, Karnataka, India</t>
+          <t>Delhi, Delhi, India</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>94/100 — Strong match: 2–5 year band, minimum 3 years MuleSoft Anypoint Platform, API design, integration patterns and cloud deployment.</t>
+          <t>96/100 — Strong match: minimum 2+ years with MuleSoft Anypoint Platform; RAML, MUnit, SOAP/REST APIs, batch processes and relational databases are explicitly required/preferred.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>https://www.accenture.com/in-en/careers/jobdetails?id=ATCI-5378805-S1962637_en</t>
+          <t>https://in.linkedin.com/jobs/view/mulesoft-developer-at-ntt-data-north-america-4466090559</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>https://www.accenture.com/in-en/careers/jobdetails?id=ATCI-5222068-S1915736_en</t>
+          <t>https://www.accenture.com/in-en/careers/jobdetails?id=ATCI-5378805-S1962637_en</t>
         </is>
       </c>
     </row>
@@ -677,7 +677,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Chennai, Tamil Nadu, India</t>
+          <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>https://www.accenture.com/in-en/careers/jobdetails?id=ATCI-5192534-S1909174_en</t>
+          <t>https://www.accenture.com/in-en/careers/jobdetails?id=ATCI-5222068-S1915736_en</t>
         </is>
       </c>
     </row>
@@ -704,27 +704,59 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>Custom Software Engineer</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>94/100 — Strong match: 2–5 year band, minimum 3 years MuleSoft Anypoint Platform, API design, integration patterns and cloud deployment.</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.accenture.com/in-en/careers/jobdetails?id=ATCI-5192534-S1909174_en</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08 09:46 IST</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
           <t>Application Developer</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>93/100 — Strong match: 2–5 year band and minimum 3 years MuleSoft Anypoint Platform, with API design, integration, API management and cloud deployment.</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>https://www.accenture.com/in-en/careers/jobdetails?id=ATCI-5106832-S1903314_en</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F9"/>
+  <autoFilter ref="A1:F10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MuleSoft_Job_Tracker.xlsx
+++ b/MuleSoft_Job_Tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet name="MuleSoft Jobs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'MuleSoft Jobs'!$A$1:$F$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'MuleSoft Jobs'!$A$1:$F$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -470,17 +470,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08 23:25 IST</t>
+          <t>2026-10-09 14:53 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>API Management Platform | Mulesoft</t>
+          <t>What is MuleSoft used for? Features, Use Cases and Managed iPaaS ...</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>API Management Platform | Mulesoft</t>
+          <t>What is MuleSoft used for? Features, Use Cases and Managed iPaaS ...</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -495,24 +495,24 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>https://mulesoft.com/api/management</t>
+          <t>https://oneio.cloud/blog/what-is-mulesoft-used-for</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08 13:40 IST</t>
+          <t>2026-10-08 23:25 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Enterprise Integration | Anypoint Platform | Mulesoft</t>
+          <t>API Management Platform | Mulesoft</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Enterprise Integration | Anypoint Platform | Mulesoft</t>
+          <t>API Management Platform | Mulesoft</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -527,39 +527,39 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>https://mulesoft.com/platform/enterprise-integration</t>
+          <t>https://mulesoft.com/api/management</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08 09:46 IST</t>
+          <t>2026-10-08 13:40 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>PwC Acceleration Center India</t>
+          <t>Enterprise Integration | Anypoint Platform | Mulesoft</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>MuleSoft Developer - Associate</t>
+          <t>Enterprise Integration | Anypoint Platform | Mulesoft</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru East, Karnataka, India</t>
+          <t>India / verify posting</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>98/100 — Excellent match: 2+ years required; Mule 4, RAML, API-led connectivity, DataWeave 2.0, Anypoint Platform, CloudHub, MUnit, SFTP/HTTP/SOAP/database connectors and API security.</t>
+          <t>47/100 — Matched profile skills: mulesoft, anypoint. Score 47/100.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/mulesoft-developer-associate-at-pwc-acceleration-center-india-4458071876</t>
+          <t>https://mulesoft.com/platform/enterprise-integration</t>
         </is>
       </c>
     </row>
@@ -581,17 +581,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Chennai, Tamil Nadu, India</t>
+          <t>Bengaluru East, Karnataka, India</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>98/100 — Excellent match: 2+ years required and the posting explicitly lists Mule 4, RAML, API-led connectivity, DataWeave 2.0, Anypoint Platform, MUnit and enterprise connectors.</t>
+          <t>98/100 — Excellent match: 2+ years required; Mule 4, RAML, API-led connectivity, DataWeave 2.0, Anypoint Platform, CloudHub, MUnit, SFTP/HTTP/SOAP/database connectors and API security.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/mulesoft-developer-associate-at-pwc-acceleration-center-india-4470181194</t>
+          <t>https://in.linkedin.com/jobs/view/mulesoft-developer-associate-at-pwc-acceleration-center-india-4458071876</t>
         </is>
       </c>
     </row>
@@ -603,27 +603,27 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>NTT DATA North America</t>
+          <t>PwC Acceleration Center India</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Mulesoft Developer</t>
+          <t>MuleSoft Developer - Associate</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Delhi, Delhi, India</t>
+          <t>Chennai, Tamil Nadu, India</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>96/100 — Strong match: minimum 2+ years with MuleSoft Anypoint Platform; RAML, MUnit, SOAP/REST APIs, batch processes and relational databases are explicitly required/preferred.</t>
+          <t>98/100 — Excellent match: 2+ years required and the posting explicitly lists Mule 4, RAML, API-led connectivity, DataWeave 2.0, Anypoint Platform, MUnit and enterprise connectors.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/mulesoft-developer-at-ntt-data-north-america-4466090559</t>
+          <t>https://in.linkedin.com/jobs/view/mulesoft-developer-associate-at-pwc-acceleration-center-india-4470181194</t>
         </is>
       </c>
     </row>
@@ -635,27 +635,27 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>NTT DATA North America</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Custom Software Engineer</t>
+          <t>Mulesoft Developer</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru, Karnataka, India</t>
+          <t>Delhi, Delhi, India</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>94/100 — Strong match: 2–5 year band, minimum 3 years MuleSoft Anypoint Platform, API design, integration patterns and cloud deployment.</t>
+          <t>96/100 — Strong match: minimum 2+ years with MuleSoft Anypoint Platform; RAML, MUnit, SOAP/REST APIs, batch processes and relational databases are explicitly required/preferred.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>https://www.accenture.com/in-en/careers/jobdetails?id=ATCI-5378805-S1962637_en</t>
+          <t>https://in.linkedin.com/jobs/view/mulesoft-developer-at-ntt-data-north-america-4466090559</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>https://www.accenture.com/in-en/careers/jobdetails?id=ATCI-5222068-S1915736_en</t>
+          <t>https://www.accenture.com/in-en/careers/jobdetails?id=ATCI-5378805-S1962637_en</t>
         </is>
       </c>
     </row>
@@ -709,7 +709,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Chennai, Tamil Nadu, India</t>
+          <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>https://www.accenture.com/in-en/careers/jobdetails?id=ATCI-5192534-S1909174_en</t>
+          <t>https://www.accenture.com/in-en/careers/jobdetails?id=ATCI-5222068-S1915736_en</t>
         </is>
       </c>
     </row>
@@ -736,27 +736,59 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>Custom Software Engineer</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>94/100 — Strong match: 2–5 year band, minimum 3 years MuleSoft Anypoint Platform, API design, integration patterns and cloud deployment.</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.accenture.com/in-en/careers/jobdetails?id=ATCI-5192534-S1909174_en</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08 09:46 IST</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
           <t>Application Developer</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>93/100 — Strong match: 2–5 year band and minimum 3 years MuleSoft Anypoint Platform, with API design, integration, API management and cloud deployment.</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>https://www.accenture.com/in-en/careers/jobdetails?id=ATCI-5106832-S1903314_en</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F10"/>
+  <autoFilter ref="A1:F11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>